--- a/simulacaoes_/custo_robustez_C13/_lote_casos.xlsx
+++ b/simulacaoes_/custo_robustez_C13/_lote_casos.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,212 +417,212 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Comprimento das longarinas (cm)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Largura da pista disponível para longarinas (cm)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>['Circular']</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Tipo de seção do tabuleiro</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Carga permanente atuante no tabuleiro (kN/m²) excluso peso próprio (kPa)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Carga por roda (kN) (kN)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Carga de multidão (kN/m²) (kPa)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Distância entre eixos (m) do veículo tipo (m)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Classe de carregamento</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Classe de madeira</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Classe de umidade</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>γg - Carga permanente</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>γq - Carga variável</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>γwc - Cisalhamento</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>γwf - Flexão</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ψ2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Coeficiente para fluência Tabela 20 NBR 7190</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Percentual de robustez</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Densidade da madeira (kg/m³) da longarina (kg/m³)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Resistência característica à flexão (MPa) da longarina (MPa)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Resistência característica ao cisalhamento (MPa) da longarina (MPa)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Módulo de elasticidade à flexão (GPa) da longarina (GPa)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Densidade da madeira (kg/m³) do tabuleiro (kg/m³)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Resistência característica à flexão (MPa) do tabuleiro (MPa)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cfg_d_min</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>cfg_d_max</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>cfg_bw_min</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>cfg_bw_max</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>cfg_h_min</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>cfg_h_max</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>cfg_esp_long_min</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>cfg_esp_long_max</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>cfg_esp_tab_min</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>cfg_esp_tab_max</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>cfg_pop_size</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>cfg_n_gen</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>cfg_n_checagens</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>cfg_sobol</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>cfg_sobol_n_samples</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>cfg_ativo</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>cfg_subdiretorio</t>
         </is>

--- a/simulacaoes_/custo_robustez_C13/_lote_casos.xlsx
+++ b/simulacaoes_/custo_robustez_C13/_lote_casos.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,216 +425,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP5"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Comprimento das longarinas (cm)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Largura da pista disponível para longarinas (cm)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>['Circular']</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Tipo de seção do tabuleiro</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Carga permanente atuante no tabuleiro (kN/m²) excluso peso próprio (kPa)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Carga por roda (kN) (kN)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Carga de multidão (kN/m²) (kPa)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Distância entre eixos (m) do veículo tipo (m)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Classe de carregamento</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Classe de madeira</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Classe de umidade</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>γg - Carga permanente</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>γq - Carga variável</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>γwc - Cisalhamento</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>γwf - Flexão</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ψ2</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Coeficiente para fluência Tabela 20 NBR 7190</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Percentual de robustez</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Densidade da madeira (kg/m³) da longarina (kg/m³)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Resistência característica à flexão (MPa) da longarina (MPa)</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Resistência característica ao cisalhamento (MPa) da longarina (MPa)</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Módulo de elasticidade à flexão (GPa) da longarina (GPa)</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Densidade da madeira (kg/m³) do tabuleiro (kg/m³)</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Resistência característica à flexão (MPa) do tabuleiro (MPa)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>cfg_d_min</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>cfg_d_max</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>cfg_bw_min</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>cfg_bw_max</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>cfg_h_min</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>cfg_h_max</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_long_min</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_long_max</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_tab_min</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_tab_max</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>cfg_pop_size</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>cfg_n_gen</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>cfg_n_checagens</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>cfg_sobol</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cfg_sobol_n_samples</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>cfg_ativo</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>cfg_subdiretorio</t>
         </is>
@@ -767,7 +779,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rho025</t>
+          <t>rho050</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -830,7 +842,7 @@
         <v>0.8</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
         <v>750</v>
@@ -903,7 +915,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rho050</t>
+          <t>rho100</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -966,7 +978,7 @@
         <v>0.8</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
         <v>750</v>
@@ -1039,7 +1051,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rho100</t>
+          <t>rho150</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1102,7 +1114,7 @@
         <v>0.8</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="n">
         <v>750</v>
@@ -1171,6 +1183,142 @@
         <v>1</v>
       </c>
       <c r="AP5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rho200</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>450</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Circular</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Retangular</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>curta duração</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>madeira natural</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="n">
+        <v>750</v>
+      </c>
+      <c r="U6" t="n">
+        <v>40</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>300</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="AO6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
